--- a/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-en_sample.xlsx
+++ b/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-en_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tools/ecuacion-tool-housekeep-db/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4D10B3-A4DE-C348-8C3F-9F2D33DD8B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC402427-3A73-9142-B457-C5035579DDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6580" yWindow="500" windowWidth="28800" windowHeight="16640" xr2:uid="{8AED4C0F-E98F-E547-A0B0-59373B747A30}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16600" activeTab="3" xr2:uid="{8AED4C0F-E98F-E547-A0B0-59373B747A30}"/>
   </bookViews>
   <sheets>
     <sheet name="change log" sheetId="8" r:id="rId1"/>
@@ -532,20 +532,20 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -564,6 +564,195 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="游ゴシック"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -882,150 +1071,6 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
@@ -1171,129 +1216,84 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
         <charset val="128"/>
         <scheme val="minor"/>
       </font>
@@ -1488,104 +1488,104 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{22FC8765-21CB-4449-8794-6F7BB0DF5CF4}" name="テーブル5" displayName="テーブル5" ref="A3:D5" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{22FC8765-21CB-4449-8794-6F7BB0DF5CF4}" name="テーブル5" displayName="テーブル5" ref="A3:D5" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
   <autoFilter ref="A3:D5" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E4142994-3892-C340-9A65-88F80365D8CE}" name="Date" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{35BACA5E-E809-0844-BAB8-78CB7B6B343E}" name="Version" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{C4E826C9-5641-E048-9706-B0754516BA47}" name="Notes" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{10D446C7-4721-E74C-863B-894EBEBABA4B}" name="Updated By" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{E4142994-3892-C340-9A65-88F80365D8CE}" name="Date" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{35BACA5E-E809-0844-BAB8-78CB7B6B343E}" name="Version" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{C4E826C9-5641-E048-9706-B0754516BA47}" name="Notes" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{10D446C7-4721-E74C-863B-894EBEBABA4B}" name="Updated By" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{24155060-B8ED-8845-8CC4-DA9C5F0847AB}" name="テーブル4" displayName="テーブル4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{24155060-B8ED-8845-8CC4-DA9C5F0847AB}" name="テーブル4" displayName="テーブル4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A1:B3" xr:uid="{24155060-B8ED-8845-8CC4-DA9C5F0847AB}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{98E4E7E5-8F2D-A64D-A202-DFFC12164331}" name="item" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{E3BF9435-59E2-8948-93E9-5462EEBA2F6D}" name="value" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{98E4E7E5-8F2D-A64D-A202-DFFC12164331}" name="item" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{E3BF9435-59E2-8948-93E9-5462EEBA2F6D}" name="value" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DD7B5D78-5E9B-DE4B-B691-1DF452AB1374}" name="テーブル3" displayName="テーブル3" ref="A5:I6" insertRow="1" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DD7B5D78-5E9B-DE4B-B691-1DF452AB1374}" name="テーブル3" displayName="テーブル3" ref="A5:I6" insertRow="1" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A5:I6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{6F9607F2-5B3B-AC43-9B81-3332FF1A0DAD}" name="DB Connection ID" dataDxfId="30" dataCellStyle="標準 2"/>
-    <tableColumn id="2" xr3:uid="{EB1F7206-30E2-EA43-A8CF-9AD4F9A14E33}" name="Driver Name" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{4D55D82B-BDD3-2B46-A21D-0450B9F1910B}" name="Connection URL: Protocol" dataDxfId="28" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{84D0845B-C5EE-9047-A1AB-EE336A75EBAD}" name="Connection URL: Server" dataDxfId="27" dataCellStyle="標準 2"/>
-    <tableColumn id="5" xr3:uid="{6197D9F5-186B-D44E-ADCB-89378D8B3702}" name="Connection URL: Port" dataDxfId="26" dataCellStyle="標準 2"/>
-    <tableColumn id="6" xr3:uid="{26B865D4-D13A-9C4C-B104-C634122F988F}" name="Connection URL: Database" dataDxfId="25" dataCellStyle="標準 2"/>
-    <tableColumn id="7" xr3:uid="{046864C3-26A2-7B44-B07A-EAB68FAF2EEA}" name="Connection URL: Schema" dataDxfId="24" dataCellStyle="標準 2"/>
-    <tableColumn id="8" xr3:uid="{4A5FE8C4-A0F3-3E4A-9BB5-642C226504CF}" name="Username" dataDxfId="23" dataCellStyle="標準 2"/>
-    <tableColumn id="9" xr3:uid="{6A963E93-AA2B-944F-A127-0CD6F7E61369}" name="Password" dataDxfId="22" dataCellStyle="標準 2"/>
+    <tableColumn id="1" xr3:uid="{6F9607F2-5B3B-AC43-9B81-3332FF1A0DAD}" name="DB Connection ID" dataDxfId="54" dataCellStyle="標準 2"/>
+    <tableColumn id="2" xr3:uid="{EB1F7206-30E2-EA43-A8CF-9AD4F9A14E33}" name="Driver Name" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{4D55D82B-BDD3-2B46-A21D-0450B9F1910B}" name="Connection URL: Protocol" dataDxfId="52" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{84D0845B-C5EE-9047-A1AB-EE336A75EBAD}" name="Connection URL: Server" dataDxfId="51" dataCellStyle="標準 2"/>
+    <tableColumn id="5" xr3:uid="{6197D9F5-186B-D44E-ADCB-89378D8B3702}" name="Connection URL: Port" dataDxfId="50" dataCellStyle="標準 2"/>
+    <tableColumn id="6" xr3:uid="{26B865D4-D13A-9C4C-B104-C634122F988F}" name="Connection URL: Database" dataDxfId="49" dataCellStyle="標準 2"/>
+    <tableColumn id="7" xr3:uid="{046864C3-26A2-7B44-B07A-EAB68FAF2EEA}" name="Connection URL: Schema" dataDxfId="48" dataCellStyle="標準 2"/>
+    <tableColumn id="8" xr3:uid="{4A5FE8C4-A0F3-3E4A-9BB5-642C226504CF}" name="Username" dataDxfId="47" dataCellStyle="標準 2"/>
+    <tableColumn id="9" xr3:uid="{6A963E93-AA2B-944F-A127-0CD6F7E61369}" name="Password" dataDxfId="46" dataCellStyle="標準 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61C29F33-44CC-B14C-8562-09C29609B4D7}" name="テーブル32" displayName="テーブル32" ref="A5:O6" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61C29F33-44CC-B14C-8562-09C29609B4D7}" name="テーブル32" displayName="テーブル32" ref="A5:O6" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="A5:O6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{CBD51E9F-618C-754C-8BA6-0B46FCE3F82F}" name="Task ID" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{5E33A481-4C3C-A049-B253-3EC944DDB6EC}" name="DB Connection ID" dataDxfId="18" dataCellStyle="標準 2"/>
-    <tableColumn id="2" xr3:uid="{AADC801E-ABC4-9E4F-8EFF-3383030B2A4B}" name="Soft / Hard Delete" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{C9A2944C-947B-B844-AE98-12A7D9A1D364}" name="Soft / Hard Delete (internal value)" dataDxfId="16">
+    <tableColumn id="1" xr3:uid="{CBD51E9F-618C-754C-8BA6-0B46FCE3F82F}" name="Task ID" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{5E33A481-4C3C-A049-B253-3EC944DDB6EC}" name="DB Connection ID" dataDxfId="32" dataCellStyle="標準 2"/>
+    <tableColumn id="2" xr3:uid="{AADC801E-ABC4-9E4F-8EFF-3383030B2A4B}" name="Soft / Hard Delete" dataDxfId="31"/>
+    <tableColumn id="15" xr3:uid="{C9A2944C-947B-B844-AE98-12A7D9A1D364}" name="Soft / Hard Delete (internal value)" dataDxfId="30">
       <calculatedColumnFormula array="1">_xlfn.IFS(テーブル32[[#This Row],[Soft / Hard Delete]]="Soft Delete","SOFT_DELETE",テーブル32[[#This Row],[Soft / Hard Delete]]="Hard Delete","HARD_DELETE",TRUE,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6C98AD64-A3D3-F44E-A881-8EFCEA1F9F67}" name="Table Name" dataDxfId="15" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{A38A3149-447A-8548-9729-49CE9E074B36}" name="ID Column Name" dataDxfId="14" dataCellStyle="標準 2"/>
-    <tableColumn id="10" xr3:uid="{B15AF0F8-272C-B943-9D75-81A8797BC598}" name="ID Column Literal Symbol" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{6FE6A1FF-15C9-7545-B254-7B2C29EF168D}" name="Expiration Check: Timestamp Column Name" dataDxfId="12" dataCellStyle="標準 2"/>
-    <tableColumn id="11" xr3:uid="{BF075527-A2E7-834B-AD05-1A2D9E3BA0AD}" name="Expiration Check: Timestamp Column Data Type" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{94EB7746-8D75-EE47-A2F3-81D397D26AE1}" name="Expiration Check: Validity Days" dataDxfId="10" dataCellStyle="標準 2"/>
-    <tableColumn id="7" xr3:uid="{62ADB4F3-1C59-7F4B-819E-B49B0ABB889C}" name="Soft Delete Column Name" dataDxfId="9" dataCellStyle="標準 2"/>
-    <tableColumn id="8" xr3:uid="{0EB6A694-7E00-B64C-AF69-22B6C7E1C560}" name="Soft Delete: Update Timestamp Column Name" dataDxfId="8" dataCellStyle="標準 2"/>
-    <tableColumn id="9" xr3:uid="{0A6924E1-C0CB-AF40-A208-E0E96A257245}" name="Soft Delete: Update User ID Column Name" dataDxfId="7" dataCellStyle="標準 2"/>
-    <tableColumn id="14" xr3:uid="{93BF3B4F-D2E8-A640-A768-A230439878D9}" name="Soft Delete: Update User ID Column Literal Symbol" dataDxfId="6" dataCellStyle="標準 2"/>
-    <tableColumn id="13" xr3:uid="{DE6ACC44-9137-0840-9711-E0D04FCC851F}" name="Soft Delete: Update User ID Column Value" dataDxfId="5" dataCellStyle="標準 2"/>
+    <tableColumn id="3" xr3:uid="{6C98AD64-A3D3-F44E-A881-8EFCEA1F9F67}" name="Table Name" dataDxfId="29" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{A38A3149-447A-8548-9729-49CE9E074B36}" name="ID Column Name" dataDxfId="28" dataCellStyle="標準 2"/>
+    <tableColumn id="10" xr3:uid="{B15AF0F8-272C-B943-9D75-81A8797BC598}" name="ID Column Literal Symbol" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{6FE6A1FF-15C9-7545-B254-7B2C29EF168D}" name="Expiration Check: Timestamp Column Name" dataDxfId="26" dataCellStyle="標準 2"/>
+    <tableColumn id="11" xr3:uid="{BF075527-A2E7-834B-AD05-1A2D9E3BA0AD}" name="Expiration Check: Timestamp Column Data Type" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{94EB7746-8D75-EE47-A2F3-81D397D26AE1}" name="Expiration Check: Validity Days" dataDxfId="24" dataCellStyle="標準 2"/>
+    <tableColumn id="7" xr3:uid="{62ADB4F3-1C59-7F4B-819E-B49B0ABB889C}" name="Soft Delete Column Name" dataDxfId="23" dataCellStyle="標準 2"/>
+    <tableColumn id="8" xr3:uid="{0EB6A694-7E00-B64C-AF69-22B6C7E1C560}" name="Soft Delete: Update Timestamp Column Name" dataDxfId="22" dataCellStyle="標準 2"/>
+    <tableColumn id="9" xr3:uid="{0A6924E1-C0CB-AF40-A208-E0E96A257245}" name="Soft Delete: Update User ID Column Name" dataDxfId="21" dataCellStyle="標準 2"/>
+    <tableColumn id="14" xr3:uid="{93BF3B4F-D2E8-A640-A768-A230439878D9}" name="Soft Delete: Update User ID Column Literal Symbol" dataDxfId="20" dataCellStyle="標準 2"/>
+    <tableColumn id="13" xr3:uid="{DE6ACC44-9137-0840-9711-E0D04FCC851F}" name="Soft Delete: Update User ID Column Value" dataDxfId="19" dataCellStyle="標準 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBD8E589-22D9-8541-A9D6-F03C8FC47C4E}" name="テーブル323" displayName="テーブル323" ref="A5:D6" insertRow="1" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBD8E589-22D9-8541-A9D6-F03C8FC47C4E}" name="テーブル323" displayName="テーブル323" ref="A5:D6" insertRow="1" totalsRowShown="0" headerRowDxfId="18">
   <autoFilter ref="A5:D6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0B02141A-0F5F-8849-982C-6C0A6A7BEE4F}" name="Task ID" dataDxfId="3" dataCellStyle="標準 2"/>
-    <tableColumn id="12" xr3:uid="{69A08ECC-4076-9E48-8CE9-3FABB073CA81}" name="Search Condition Column Name" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{511F37DB-74E3-394C-9204-B1C6CA623CD0}" name="Search Condtion Column Literal Symbol" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{2F474AF9-6428-D446-9D8C-0FEF2C86FE1D}" name="Search Condition Column Value" dataDxfId="0" dataCellStyle="標準 2"/>
+    <tableColumn id="1" xr3:uid="{0B02141A-0F5F-8849-982C-6C0A6A7BEE4F}" name="Task ID" dataDxfId="17" dataCellStyle="標準 2"/>
+    <tableColumn id="12" xr3:uid="{69A08ECC-4076-9E48-8CE9-3FABB073CA81}" name="Search Condition Column Name" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{511F37DB-74E3-394C-9204-B1C6CA623CD0}" name="Search Condtion Column Literal Symbol" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{2F474AF9-6428-D446-9D8C-0FEF2C86FE1D}" name="Search Condition Column Value" dataDxfId="14" dataCellStyle="標準 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EE7E132-481E-3140-932F-4C153EC6948B}" name="テーブル3236" displayName="テーブル3236" ref="A5:L6" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EE7E132-481E-3140-932F-4C153EC6948B}" name="テーブル3236" displayName="テーブル3236" ref="A5:L6" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A5:L6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{65C86A53-0A13-8F47-916D-E06475BCECE3}" name="Task ID" dataDxfId="54"/>
-    <tableColumn id="12" xr3:uid="{987F2B9C-94EA-9F41-A4C1-6D7606B12BAC}" name="Related Table Process Pattern" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{B871A9E9-220D-F74C-A1C5-BED1ED6DD954}" name="Related Table Process Pattern (internal value)" dataDxfId="52">
+    <tableColumn id="1" xr3:uid="{65C86A53-0A13-8F47-916D-E06475BCECE3}" name="Task ID" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{987F2B9C-94EA-9F41-A4C1-6D7606B12BAC}" name="Related Table Process Pattern" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{B871A9E9-220D-F74C-A1C5-BED1ED6DD954}" name="Related Table Process Pattern (internal value)" dataDxfId="9">
       <calculatedColumnFormula array="1">_xlfn.IFS(テーブル3236[[#This Row],[Related Table Process Pattern]]="Delete","DELETE",テーブル3236[[#This Row],[Related Table Process Pattern]]="Check and Skip Delete","CHECK_AND_SKIP_DELETE",TRUE,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{5E73C8D1-B2FA-854B-BEBB-60B6E93A2638}" name="Target Table Column Name" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{3B40126A-13DD-E04B-A86B-9387EB6006A1}" name="Related Table Name" dataDxfId="50" dataCellStyle="標準 2"/>
-    <tableColumn id="3" xr3:uid="{59ED585B-1BCF-DB41-A333-2655E74C710D}" name="Related Table ID Column Name" dataDxfId="49" dataCellStyle="標準 2"/>
-    <tableColumn id="14" xr3:uid="{75144EA6-AFC2-3646-9A0E-DD4A2D917411}" name="Related Table ID Column Literal Symbol" dataDxfId="48" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{684AF203-54CE-5A42-8441-2636BF604DAF}" name="Soft Delete Column Name" dataDxfId="47" dataCellStyle="標準 2"/>
-    <tableColumn id="5" xr3:uid="{1D070257-74D6-6746-B460-ACB59A1770E6}" name="Soft Delete: Update Timestamp Column Name" dataDxfId="46" dataCellStyle="標準 2"/>
-    <tableColumn id="6" xr3:uid="{59287FEB-061F-B946-B814-312CDD2F482D}" name="Soft Delete: Update User ID Column Name" dataDxfId="45" dataCellStyle="標準 2"/>
-    <tableColumn id="7" xr3:uid="{E0734288-8DC3-C342-98A6-DBC50A55CEF9}" name="Soft Delete: Update User ID Column Literal Symbol" dataDxfId="44" dataCellStyle="標準 2"/>
-    <tableColumn id="8" xr3:uid="{D5E8A958-B06D-554D-B183-49DD307AC86A}" name="Soft Delete: Update User ID Column Value" dataDxfId="43" dataCellStyle="標準 2"/>
+    <tableColumn id="13" xr3:uid="{5E73C8D1-B2FA-854B-BEBB-60B6E93A2638}" name="Target Table Column Name" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{3B40126A-13DD-E04B-A86B-9387EB6006A1}" name="Related Table Name" dataDxfId="7" dataCellStyle="標準 2"/>
+    <tableColumn id="3" xr3:uid="{59ED585B-1BCF-DB41-A333-2655E74C710D}" name="Related Table ID Column Name" dataDxfId="6" dataCellStyle="標準 2"/>
+    <tableColumn id="14" xr3:uid="{75144EA6-AFC2-3646-9A0E-DD4A2D917411}" name="Related Table ID Column Literal Symbol" dataDxfId="5" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{684AF203-54CE-5A42-8441-2636BF604DAF}" name="Soft Delete Column Name" dataDxfId="4" dataCellStyle="標準 2"/>
+    <tableColumn id="5" xr3:uid="{1D070257-74D6-6746-B460-ACB59A1770E6}" name="Soft Delete: Update Timestamp Column Name" dataDxfId="3" dataCellStyle="標準 2"/>
+    <tableColumn id="6" xr3:uid="{59287FEB-061F-B946-B814-312CDD2F482D}" name="Soft Delete: Update User ID Column Name" dataDxfId="2" dataCellStyle="標準 2"/>
+    <tableColumn id="7" xr3:uid="{E0734288-8DC3-C342-98A6-DBC50A55CEF9}" name="Soft Delete: Update User ID Column Literal Symbol" dataDxfId="1" dataCellStyle="標準 2"/>
+    <tableColumn id="8" xr3:uid="{D5E8A958-B06D-554D-B183-49DD307AC86A}" name="Soft Delete: Update User ID Column Value" dataDxfId="0" dataCellStyle="標準 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1938,7 +1938,7 @@
       <c r="B5" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="24" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="11" t="s">
@@ -2286,20 +2286,20 @@
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
       <c r="K4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
@@ -2567,13 +2567,13 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">

--- a/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-en_sample.xlsx
+++ b/ecuacion-tool-housekeep-db/excel-format/housekeep-db_fmt-v2.0.0-en_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yosuke.tanaka/Desktop/development/git/ecuacion-tools/ecuacion-tool-housekeep-db/excel-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC402427-3A73-9142-B457-C5035579DDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B134B03E-2612-A24B-B849-1158501881D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16600" activeTab="3" xr2:uid="{8AED4C0F-E98F-E547-A0B0-59373B747A30}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16600" xr2:uid="{8AED4C0F-E98F-E547-A0B0-59373B747A30}"/>
   </bookViews>
   <sheets>
     <sheet name="change log" sheetId="8" r:id="rId1"/>
@@ -48,6 +48,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={7D829323-4655-CD44-9CAF-FB0BE1358339}</author>
+  </authors>
+  <commentList>
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{7D829323-4655-CD44-9CAF-FB0BE1358339}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Required because actual deletion specifies which record to delete by this ID column's value</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -71,18 +89,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>value</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>item</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>format-version</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Format Excel Change Log</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Updated By</t>
+  </si>
+  <si>
+    <t>DB Connection ID</t>
+  </si>
+  <si>
+    <t>Driver Name</t>
+  </si>
+  <si>
+    <t>Connection URL: Protocol</t>
+  </si>
+  <si>
+    <t>Connection URL: Port</t>
+  </si>
+  <si>
+    <t>Connection URL: Server</t>
+  </si>
+  <si>
+    <t>Connection URL: Schema</t>
+  </si>
+  <si>
+    <t>Connection URL: Database</t>
+  </si>
+  <si>
+    <t>Username</t>
   </si>
   <si>
     <t>postgresql</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>(none)</t>
@@ -94,207 +154,143 @@
     <t>LocalDateTime</t>
   </si>
   <si>
+    <t>DB Connection ID</t>
+  </si>
+  <si>
+    <t>Task ID</t>
+  </si>
+  <si>
+    <t>* Excel reader finishes reading when it finds an empty A-column cell.</t>
+  </si>
+  <si>
+    <t>Search Condition Column Name</t>
+  </si>
+  <si>
+    <t>Search Condition Column Literal Symbol</t>
+  </si>
+  <si>
+    <t>Search Condition Column Value</t>
+  </si>
+  <si>
+    <t>Target Table Column Name</t>
+  </si>
+  <si>
+    <t>Related Table Name</t>
+  </si>
+  <si>
+    <t>Related Table Process Pattern</t>
+  </si>
+  <si>
+    <t>Timestamp Column Data Type</t>
+  </si>
+  <si>
+    <t>Soft Delete: Update Timestamp Column Name</t>
+  </si>
+  <si>
+    <t>Soft Delete: Update User ID Column Name</t>
+  </si>
+  <si>
+    <t>Soft Delete: Update User ID Column Value</t>
+  </si>
+  <si>
+    <t>Connection URL: Protocol</t>
+  </si>
+  <si>
+    <t>Soft Delete: Update User ID Column Literal Symbol</t>
+  </si>
+  <si>
+    <t>Literal Symbol</t>
+  </si>
+  <si>
     <t>quotes(')</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>optional on hard delete, required on soft delete</t>
-  </si>
-  <si>
-    <t>empty on hard delete, optional on soft delete</t>
-  </si>
-  <si>
-    <t>first version</t>
+  </si>
+  <si>
+    <t>Related Table ID Column Name</t>
+  </si>
+  <si>
+    <t>Related Table ID Column Literal Symbol</t>
   </si>
   <si>
     <t>Yosuke Tanaka</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Updated By</t>
-  </si>
-  <si>
-    <t>Format Excel Cnange Log</t>
+    <t>Expiration Check: Timestamp Column Name</t>
+  </si>
+  <si>
+    <t>Expiration Check: Timestamp Column Data Type</t>
+  </si>
+  <si>
+    <t>Expiration Check: Validity Days</t>
+  </si>
+  <si>
+    <t>Soft Delete Column Name</t>
+  </si>
+  <si>
+    <t>Soft Delete: Update User ID Column Name</t>
+  </si>
+  <si>
+    <t>Soft Delete: Update User ID Column Value</t>
+  </si>
+  <si>
+    <t>Soft Delete: Update User ID Column Literal Symbol</t>
+  </si>
+  <si>
+    <t>Soft Delete: Update Timestamp Column Name</t>
+  </si>
+  <si>
+    <t>locale</t>
   </si>
   <si>
     <t>en</t>
   </si>
   <si>
-    <t>locale</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>DB Connection ID</t>
-  </si>
-  <si>
-    <t>Driver Name</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>1.3.0</t>
-  </si>
-  <si>
-    <t>* "Connection URL: schema" is needed only when the default schema (the name of the schema equal to the username)</t>
-  </si>
-  <si>
-    <t>DB connection settings</t>
+    <t>Task ID</t>
+  </si>
+  <si>
+    <t>Table Name</t>
+  </si>
+  <si>
+    <t>ID Column Name</t>
+  </si>
+  <si>
+    <t>ID Column Literal Symbol</t>
+  </si>
+  <si>
+    <t>DB Connection Settings</t>
   </si>
   <si>
     <t>Housekeep DB Settings</t>
   </si>
   <si>
-    <t>* Excel reader finishes reading when it finds an empty A-column cell.</t>
-  </si>
-  <si>
-    <t>Task ID</t>
-  </si>
-  <si>
-    <t>Table Name</t>
+    <t>Related Table Settings</t>
+  </si>
+  <si>
+    <t>Search Condition Settings</t>
   </si>
   <si>
     <t>Soft / Hard Delete</t>
   </si>
   <si>
-    <t>ID Column Name</t>
-  </si>
-  <si>
-    <t>ID Column Literal Symbol</t>
-  </si>
-  <si>
-    <t>Expiration Check: Timestamp Column Name</t>
-  </si>
-  <si>
-    <t>Connection URL: Protocol</t>
-  </si>
-  <si>
-    <t>Connection URL: Server</t>
-  </si>
-  <si>
-    <t>Connection URL: Port</t>
-  </si>
-  <si>
-    <t>Connection URL: Database</t>
-  </si>
-  <si>
-    <t>Connection URL: Schema</t>
-  </si>
-  <si>
-    <t>Expiration Check: Timestamp Column Data Type</t>
-  </si>
-  <si>
-    <t>Expiration Check: Validity Days</t>
-  </si>
-  <si>
-    <t>Soft Delete Column Name</t>
-  </si>
-  <si>
-    <t>Soft Delete: Update User ID Column Name</t>
-  </si>
-  <si>
-    <t>Soft Delete: Update Timestamp Column Name</t>
-  </si>
-  <si>
-    <t>Soft Delete: Update User ID Column Literal Symbol</t>
-  </si>
-  <si>
-    <t>Soft Delete: Update User ID Column Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  If you execute soft / hard deletion without specifing these, the record will be deleted without any expiration checks.</t>
-  </si>
-  <si>
-    <t>　</t>
-  </si>
-  <si>
-    <t>* If you specify "Soft Delete Column Name" when you hard delete, the deletion will only be performed if the specified column is "true". (Only bool type is supported for the delete flag column.)</t>
-  </si>
-  <si>
-    <t>* "Soft Delete: Update Timestamp Column Name" is specified when there is an item for which the timestamp is to be updated. The value is automatically set to the current time.</t>
-  </si>
-  <si>
-    <t>* "Expiration Check: Timestamp Column Name", "Expiration Check: Timestamp Column Data Type", and "Expiration Check: Validity Days" are optional. However, you can either leave them all empty or enter all the fields.</t>
-  </si>
-  <si>
-    <t>Related Table Settings</t>
-  </si>
-  <si>
-    <t>Related Table Process Pattern</t>
-  </si>
-  <si>
-    <t>Target Table Column Name</t>
-  </si>
-  <si>
-    <t>Literal Symbol</t>
-  </si>
-  <si>
-    <t>Timestamp Column Data Type</t>
-  </si>
-  <si>
-    <t>Related Table Name</t>
-  </si>
-  <si>
-    <t>Related Table ID Column Name</t>
-  </si>
-  <si>
-    <t>Related Table ID Column Literal Symbol</t>
-  </si>
-  <si>
-    <t>* "Soft Delete Column Name" is required if "Soft / Hard Delete" in "Housekeep DB Settings" sheet is "Soft Delete", and optional if "Hard Delete". If this item is specified in the "Hard Delete" case, the deletion will be performed only if the specified column is "true".</t>
-  </si>
-  <si>
-    <t>* "Soft Delete: Update User ID Column Name", "Soft Delete: Update User ID Column Literal Symbol", and "Soft Delete: Update User ID Column Value" are specified when there is an item for which the user ID is to be updated. Either leave all fields empty or enter all fields.</t>
-  </si>
-  <si>
-    <t>Search Condition Settings</t>
-  </si>
-  <si>
-    <t>Search Condition Column Name</t>
-  </si>
-  <si>
-    <t>Search Condtion Column Literal Symbol</t>
-  </si>
-  <si>
-    <t>Search Condition Column Value</t>
-  </si>
-  <si>
-    <t>DO NOT CHANGE</t>
-  </si>
-  <si>
     <t>Soft / Hard Delete (internal value)</t>
   </si>
   <si>
     <t>Related Table Process Pattern (internal value)</t>
   </si>
   <si>
-    <t>format-version</t>
+    <t>v2.0.0</t>
   </si>
   <si>
     <t>2.0.0</t>
   </si>
   <si>
-    <t>housekeep-db: v15
-- info sheet
-  - Delete "database" item following MySQL integration
-  - Hide sheet
-  - Delete comment in row 1</t>
+    <t>Expiration Check Items</t>
+  </si>
+  <si>
+    <t>Soft Delete Items</t>
+  </si>
+  <si>
+    <t>housekeep-db: 
+English version added</t>
   </si>
 </sst>
 </file>
@@ -384,7 +380,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,26 +404,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB7942"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD883FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -450,6 +428,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0"/>
+      </left>
+      <right style="hair">
+        <color theme="0"/>
+      </right>
+      <top style="hair">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0"/>
+      </left>
+      <right style="hair">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0"/>
+      </left>
+      <right style="hair">
+        <color theme="0"/>
+      </right>
+      <top style="hair">
+        <color theme="0"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color theme="0"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -463,7 +513,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -496,14 +546,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
@@ -514,38 +564,50 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -554,64 +616,97 @@
     <cellStyle name="標準 2" xfId="1" xr:uid="{BD6EA7D8-0FCB-0647-872F-4B8806E77649}"/>
     <cellStyle name="標準 3" xfId="3" xr:uid="{5847071D-4CD7-2041-8E1B-31F36A89F42E}"/>
   </cellStyles>
-  <dxfs count="57">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
+  <dxfs count="56">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -700,49 +795,66 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color theme="0"/>
+        </left>
+        <right style="hair">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="hair">
+          <color theme="0"/>
+        </vertical>
+        <horizontal style="hair">
+          <color theme="0"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -813,6 +925,22 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color theme="0"/>
+        </left>
+        <right style="hair">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="hair">
+          <color theme="0"/>
+        </vertical>
+        <horizontal style="hair">
+          <color theme="0"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1008,63 +1136,223 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color theme="0"/>
+        </left>
+        <right style="hair">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="hair">
+          <color theme="0"/>
+        </vertical>
+        <horizontal style="hair">
+          <color theme="0"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1076,6 +1364,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="游ゴシック"/>
+        <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
       </font>
@@ -1091,6 +1380,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="游ゴシック"/>
+        <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
       </font>
@@ -1114,14 +1404,42 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1136,225 +1454,18 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFD883FF"/>
+      <color rgb="FF9437FF"/>
+      <color rgb="FF929000"/>
+      <color rgb="FFFF2F92"/>
+      <color rgb="FFFF8AD8"/>
+      <color rgb="FFFF85FF"/>
+      <color rgb="FF521B93"/>
       <color rgb="FFAB7942"/>
     </mruColors>
   </colors>
@@ -1487,105 +1598,111 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="田中庸介" id="{78017D61-44A1-0A4F-9335-7121C27F2A1F}" userId="S::yosuke.tanaka@ecuacion.jp::d5495b55-5ca6-44f8-b4f6-a2bcc0a387d4" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{22FC8765-21CB-4449-8794-6F7BB0DF5CF4}" name="テーブル5" displayName="テーブル5" ref="A3:D5" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
-  <autoFilter ref="A3:D5" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{22FC8765-21CB-4449-8794-6F7BB0DF5CF4}" name="テーブル5" displayName="テーブル5" ref="A3:D4" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A3:D4" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E4142994-3892-C340-9A65-88F80365D8CE}" name="Date" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{35BACA5E-E809-0844-BAB8-78CB7B6B343E}" name="Version" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{C4E826C9-5641-E048-9706-B0754516BA47}" name="Notes" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{10D446C7-4721-E74C-863B-894EBEBABA4B}" name="Updated By" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{E4142994-3892-C340-9A65-88F80365D8CE}" name="Date" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{35BACA5E-E809-0844-BAB8-78CB7B6B343E}" name="Version" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{C4E826C9-5641-E048-9706-B0754516BA47}" name="Notes" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{10D446C7-4721-E74C-863B-894EBEBABA4B}" name="Updated By" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{24155060-B8ED-8845-8CC4-DA9C5F0847AB}" name="テーブル4" displayName="テーブル4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{24155060-B8ED-8845-8CC4-DA9C5F0847AB}" name="テーブル4" displayName="テーブル4" ref="A1:B3" totalsRowShown="0" headerRowDxfId="51">
   <autoFilter ref="A1:B3" xr:uid="{24155060-B8ED-8845-8CC4-DA9C5F0847AB}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{98E4E7E5-8F2D-A64D-A202-DFFC12164331}" name="item" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{E3BF9435-59E2-8948-93E9-5462EEBA2F6D}" name="value" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{98E4E7E5-8F2D-A64D-A202-DFFC12164331}" name="item" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{E3BF9435-59E2-8948-93E9-5462EEBA2F6D}" name="value" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DD7B5D78-5E9B-DE4B-B691-1DF452AB1374}" name="テーブル3" displayName="テーブル3" ref="A5:I6" insertRow="1" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A5:I6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DD7B5D78-5E9B-DE4B-B691-1DF452AB1374}" name="テーブル3" displayName="テーブル3" ref="A4:I5" insertRow="1" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+  <autoFilter ref="A4:I5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{6F9607F2-5B3B-AC43-9B81-3332FF1A0DAD}" name="DB Connection ID" dataDxfId="54" dataCellStyle="標準 2"/>
-    <tableColumn id="2" xr3:uid="{EB1F7206-30E2-EA43-A8CF-9AD4F9A14E33}" name="Driver Name" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{4D55D82B-BDD3-2B46-A21D-0450B9F1910B}" name="Connection URL: Protocol" dataDxfId="52" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{84D0845B-C5EE-9047-A1AB-EE336A75EBAD}" name="Connection URL: Server" dataDxfId="51" dataCellStyle="標準 2"/>
-    <tableColumn id="5" xr3:uid="{6197D9F5-186B-D44E-ADCB-89378D8B3702}" name="Connection URL: Port" dataDxfId="50" dataCellStyle="標準 2"/>
-    <tableColumn id="6" xr3:uid="{26B865D4-D13A-9C4C-B104-C634122F988F}" name="Connection URL: Database" dataDxfId="49" dataCellStyle="標準 2"/>
-    <tableColumn id="7" xr3:uid="{046864C3-26A2-7B44-B07A-EAB68FAF2EEA}" name="Connection URL: Schema" dataDxfId="48" dataCellStyle="標準 2"/>
-    <tableColumn id="8" xr3:uid="{4A5FE8C4-A0F3-3E4A-9BB5-642C226504CF}" name="Username" dataDxfId="47" dataCellStyle="標準 2"/>
-    <tableColumn id="9" xr3:uid="{6A963E93-AA2B-944F-A127-0CD6F7E61369}" name="Password" dataDxfId="46" dataCellStyle="標準 2"/>
+    <tableColumn id="1" xr3:uid="{6F9607F2-5B3B-AC43-9B81-3332FF1A0DAD}" name="DB Connection ID" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{EB1F7206-30E2-EA43-A8CF-9AD4F9A14E33}" name="Driver Name" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{4D55D82B-BDD3-2B46-A21D-0450B9F1910B}" name="Connection URL: Protocol" dataDxfId="44" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{84D0845B-C5EE-9047-A1AB-EE336A75EBAD}" name="Connection URL: Server" dataDxfId="43" dataCellStyle="標準 2"/>
+    <tableColumn id="5" xr3:uid="{6197D9F5-186B-D44E-ADCB-89378D8B3702}" name="Connection URL: Port" dataDxfId="42" dataCellStyle="標準 2"/>
+    <tableColumn id="6" xr3:uid="{26B865D4-D13A-9C4C-B104-C634122F988F}" name="Connection URL: Database" dataDxfId="41" dataCellStyle="標準 2"/>
+    <tableColumn id="7" xr3:uid="{046864C3-26A2-7B44-B07A-EAB68FAF2EEA}" name="Connection URL: Schema" dataDxfId="40" dataCellStyle="標準 2"/>
+    <tableColumn id="8" xr3:uid="{4A5FE8C4-A0F3-3E4A-9BB5-642C226504CF}" name="Username" dataDxfId="39" dataCellStyle="標準 2"/>
+    <tableColumn id="9" xr3:uid="{6A963E93-AA2B-944F-A127-0CD6F7E61369}" name="Password" dataDxfId="38" dataCellStyle="標準 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61C29F33-44CC-B14C-8562-09C29609B4D7}" name="テーブル32" displayName="テーブル32" ref="A5:O6" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
-  <autoFilter ref="A5:O6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61C29F33-44CC-B14C-8562-09C29609B4D7}" name="テーブル32" displayName="テーブル32" ref="A4:O5" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+  <autoFilter ref="A4:O5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{CBD51E9F-618C-754C-8BA6-0B46FCE3F82F}" name="Task ID" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{5E33A481-4C3C-A049-B253-3EC944DDB6EC}" name="DB Connection ID" dataDxfId="32" dataCellStyle="標準 2"/>
-    <tableColumn id="2" xr3:uid="{AADC801E-ABC4-9E4F-8EFF-3383030B2A4B}" name="Soft / Hard Delete" dataDxfId="31"/>
-    <tableColumn id="15" xr3:uid="{C9A2944C-947B-B844-AE98-12A7D9A1D364}" name="Soft / Hard Delete (internal value)" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{CBD51E9F-618C-754C-8BA6-0B46FCE3F82F}" name="Task ID" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{5E33A481-4C3C-A049-B253-3EC944DDB6EC}" name="DB Connection ID" dataDxfId="34" dataCellStyle="標準 2"/>
+    <tableColumn id="2" xr3:uid="{AADC801E-ABC4-9E4F-8EFF-3383030B2A4B}" name="Soft / Hard Delete" dataDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{F58118F0-6716-6C42-853A-3FBAEE07F4E8}" name="Soft / Hard Delete (internal value)" dataDxfId="32">
       <calculatedColumnFormula array="1">_xlfn.IFS(テーブル32[[#This Row],[Soft / Hard Delete]]="Soft Delete","SOFT_DELETE",テーブル32[[#This Row],[Soft / Hard Delete]]="Hard Delete","HARD_DELETE",TRUE,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6C98AD64-A3D3-F44E-A881-8EFCEA1F9F67}" name="Table Name" dataDxfId="29" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{A38A3149-447A-8548-9729-49CE9E074B36}" name="ID Column Name" dataDxfId="28" dataCellStyle="標準 2"/>
-    <tableColumn id="10" xr3:uid="{B15AF0F8-272C-B943-9D75-81A8797BC598}" name="ID Column Literal Symbol" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{6FE6A1FF-15C9-7545-B254-7B2C29EF168D}" name="Expiration Check: Timestamp Column Name" dataDxfId="26" dataCellStyle="標準 2"/>
-    <tableColumn id="11" xr3:uid="{BF075527-A2E7-834B-AD05-1A2D9E3BA0AD}" name="Expiration Check: Timestamp Column Data Type" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{94EB7746-8D75-EE47-A2F3-81D397D26AE1}" name="Expiration Check: Validity Days" dataDxfId="24" dataCellStyle="標準 2"/>
-    <tableColumn id="7" xr3:uid="{62ADB4F3-1C59-7F4B-819E-B49B0ABB889C}" name="Soft Delete Column Name" dataDxfId="23" dataCellStyle="標準 2"/>
-    <tableColumn id="8" xr3:uid="{0EB6A694-7E00-B64C-AF69-22B6C7E1C560}" name="Soft Delete: Update Timestamp Column Name" dataDxfId="22" dataCellStyle="標準 2"/>
-    <tableColumn id="9" xr3:uid="{0A6924E1-C0CB-AF40-A208-E0E96A257245}" name="Soft Delete: Update User ID Column Name" dataDxfId="21" dataCellStyle="標準 2"/>
-    <tableColumn id="14" xr3:uid="{93BF3B4F-D2E8-A640-A768-A230439878D9}" name="Soft Delete: Update User ID Column Literal Symbol" dataDxfId="20" dataCellStyle="標準 2"/>
-    <tableColumn id="13" xr3:uid="{DE6ACC44-9137-0840-9711-E0D04FCC851F}" name="Soft Delete: Update User ID Column Value" dataDxfId="19" dataCellStyle="標準 2"/>
+    <tableColumn id="3" xr3:uid="{6C98AD64-A3D3-F44E-A881-8EFCEA1F9F67}" name="Table Name" dataDxfId="31" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{A38A3149-447A-8548-9729-49CE9E074B36}" name="ID Column Name" dataDxfId="30" dataCellStyle="標準 2"/>
+    <tableColumn id="10" xr3:uid="{B15AF0F8-272C-B943-9D75-81A8797BC598}" name="ID Column Literal Symbol" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{6FE6A1FF-15C9-7545-B254-7B2C29EF168D}" name="Expiration Check: Timestamp Column Name" dataDxfId="28" dataCellStyle="標準 2"/>
+    <tableColumn id="11" xr3:uid="{BF075527-A2E7-834B-AD05-1A2D9E3BA0AD}" name="Expiration Check: Timestamp Column Data Type" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{94EB7746-8D75-EE47-A2F3-81D397D26AE1}" name="Expiration Check: Validity Days" dataDxfId="26" dataCellStyle="標準 2"/>
+    <tableColumn id="7" xr3:uid="{62ADB4F3-1C59-7F4B-819E-B49B0ABB889C}" name="Soft Delete Column Name" dataDxfId="25" dataCellStyle="標準 2"/>
+    <tableColumn id="8" xr3:uid="{0EB6A694-7E00-B64C-AF69-22B6C7E1C560}" name="Soft Delete: Update Timestamp Column Name" dataDxfId="24" dataCellStyle="標準 2"/>
+    <tableColumn id="9" xr3:uid="{0A6924E1-C0CB-AF40-A208-E0E96A257245}" name="Soft Delete: Update User ID Column Name" dataDxfId="23" dataCellStyle="標準 2"/>
+    <tableColumn id="14" xr3:uid="{93BF3B4F-D2E8-A640-A768-A230439878D9}" name="Soft Delete: Update User ID Column Literal Symbol" dataDxfId="22" dataCellStyle="標準 2"/>
+    <tableColumn id="13" xr3:uid="{DE6ACC44-9137-0840-9711-E0D04FCC851F}" name="Soft Delete: Update User ID Column Value" dataDxfId="21" dataCellStyle="標準 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBD8E589-22D9-8541-A9D6-F03C8FC47C4E}" name="テーブル323" displayName="テーブル323" ref="A5:D6" insertRow="1" totalsRowShown="0" headerRowDxfId="18">
-  <autoFilter ref="A5:D6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBD8E589-22D9-8541-A9D6-F03C8FC47C4E}" name="テーブル323" displayName="テーブル323" ref="A4:D5" insertRow="1" totalsRowShown="0" headerRowDxfId="20">
+  <autoFilter ref="A4:D5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0B02141A-0F5F-8849-982C-6C0A6A7BEE4F}" name="Task ID" dataDxfId="17" dataCellStyle="標準 2"/>
-    <tableColumn id="12" xr3:uid="{69A08ECC-4076-9E48-8CE9-3FABB073CA81}" name="Search Condition Column Name" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{511F37DB-74E3-394C-9204-B1C6CA623CD0}" name="Search Condtion Column Literal Symbol" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{2F474AF9-6428-D446-9D8C-0FEF2C86FE1D}" name="Search Condition Column Value" dataDxfId="14" dataCellStyle="標準 2"/>
+    <tableColumn id="1" xr3:uid="{0B02141A-0F5F-8849-982C-6C0A6A7BEE4F}" name="Task ID" dataDxfId="19" dataCellStyle="標準 2"/>
+    <tableColumn id="12" xr3:uid="{69A08ECC-4076-9E48-8CE9-3FABB073CA81}" name="Search Condition Column Name" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{511F37DB-74E3-394C-9204-B1C6CA623CD0}" name="Search Condition Column Literal Symbol" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{2F474AF9-6428-D446-9D8C-0FEF2C86FE1D}" name="Search Condition Column Value" dataDxfId="16" dataCellStyle="標準 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EE7E132-481E-3140-932F-4C153EC6948B}" name="テーブル3236" displayName="テーブル3236" ref="A5:L6" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A5:L6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5EE7E132-481E-3140-932F-4C153EC6948B}" name="テーブル3236" displayName="テーブル3236" ref="A4:L5" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A4:L5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{65C86A53-0A13-8F47-916D-E06475BCECE3}" name="Task ID" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{987F2B9C-94EA-9F41-A4C1-6D7606B12BAC}" name="Related Table Process Pattern" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{B871A9E9-220D-F74C-A1C5-BED1ED6DD954}" name="Related Table Process Pattern (internal value)" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{65C86A53-0A13-8F47-916D-E06475BCECE3}" name="Task ID" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{987F2B9C-94EA-9F41-A4C1-6D7606B12BAC}" name="Related Table Process Pattern" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{4A3F5F45-559C-3B48-8E59-FDBCE79B21C8}" name="Related Table Process Pattern (internal value)" dataDxfId="11">
       <calculatedColumnFormula array="1">_xlfn.IFS(テーブル3236[[#This Row],[Related Table Process Pattern]]="Delete","DELETE",テーブル3236[[#This Row],[Related Table Process Pattern]]="Check and Skip Delete","CHECK_AND_SKIP_DELETE",TRUE,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{5E73C8D1-B2FA-854B-BEBB-60B6E93A2638}" name="Target Table Column Name" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{3B40126A-13DD-E04B-A86B-9387EB6006A1}" name="Related Table Name" dataDxfId="7" dataCellStyle="標準 2"/>
-    <tableColumn id="3" xr3:uid="{59ED585B-1BCF-DB41-A333-2655E74C710D}" name="Related Table ID Column Name" dataDxfId="6" dataCellStyle="標準 2"/>
-    <tableColumn id="14" xr3:uid="{75144EA6-AFC2-3646-9A0E-DD4A2D917411}" name="Related Table ID Column Literal Symbol" dataDxfId="5" dataCellStyle="標準 2"/>
-    <tableColumn id="4" xr3:uid="{684AF203-54CE-5A42-8441-2636BF604DAF}" name="Soft Delete Column Name" dataDxfId="4" dataCellStyle="標準 2"/>
-    <tableColumn id="5" xr3:uid="{1D070257-74D6-6746-B460-ACB59A1770E6}" name="Soft Delete: Update Timestamp Column Name" dataDxfId="3" dataCellStyle="標準 2"/>
-    <tableColumn id="6" xr3:uid="{59287FEB-061F-B946-B814-312CDD2F482D}" name="Soft Delete: Update User ID Column Name" dataDxfId="2" dataCellStyle="標準 2"/>
-    <tableColumn id="7" xr3:uid="{E0734288-8DC3-C342-98A6-DBC50A55CEF9}" name="Soft Delete: Update User ID Column Literal Symbol" dataDxfId="1" dataCellStyle="標準 2"/>
-    <tableColumn id="8" xr3:uid="{D5E8A958-B06D-554D-B183-49DD307AC86A}" name="Soft Delete: Update User ID Column Value" dataDxfId="0" dataCellStyle="標準 2"/>
+    <tableColumn id="13" xr3:uid="{5E73C8D1-B2FA-854B-BEBB-60B6E93A2638}" name="Target Table Column Name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{3B40126A-13DD-E04B-A86B-9387EB6006A1}" name="Related Table Name" dataDxfId="9" dataCellStyle="標準 2"/>
+    <tableColumn id="3" xr3:uid="{59ED585B-1BCF-DB41-A333-2655E74C710D}" name="Related Table ID Column Name" dataDxfId="8" dataCellStyle="標準 2"/>
+    <tableColumn id="14" xr3:uid="{75144EA6-AFC2-3646-9A0E-DD4A2D917411}" name="Related Table ID Column Literal Symbol" dataDxfId="7" dataCellStyle="標準 2"/>
+    <tableColumn id="4" xr3:uid="{684AF203-54CE-5A42-8441-2636BF604DAF}" name="Soft Delete Column Name" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{1D070257-74D6-6746-B460-ACB59A1770E6}" name="Soft Delete: Update Timestamp Column Name" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{59287FEB-061F-B946-B814-312CDD2F482D}" name="Soft Delete: Update User ID Column Name" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{E0734288-8DC3-C342-98A6-DBC50A55CEF9}" name="Soft Delete: Update User ID Column Literal Symbol" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{D5E8A958-B06D-554D-B183-49DD307AC86A}" name="Soft Delete: Update User ID Column Value" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1886,9 +2003,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F4" dT="2024-08-31T07:19:37.97" personId="{78017D61-44A1-0A4F-9335-7121C27F2A1F}" id="{7D829323-4655-CD44-9CAF-FB0BE1358339}">
+    <text>Required because actual deletion specifies which record to delete by this ID column's value</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF07F212-59AD-6B4B-8D53-7B3A09021B62}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="4" customWidth="1"/>
@@ -1900,49 +2025,35 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
-        <v>45780</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>24</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="80" x14ac:dyDescent="0.2">
-      <c r="A5" s="23">
-        <v>46256</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>10</v>
+        <v>66</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1975,18 +2086,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2003,40 +2114,40 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="10" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2132,305 +2243,211 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A269F1A1-7AAA-9644-B9A4-2FF06B781584}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="20.1640625" style="6" customWidth="1"/>
+    <col min="2" max="9" width="20.1640625" style="6" customWidth="1"/>
     <col min="10" max="16384" width="7.5" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="26"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="H4:I4"/>
-  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3FC4779E-3CB6-784A-862F-503D20B67CED}">
-          <x14:formula1>
-            <xm:f>dropdown!$A$2:$A$20</xm:f>
-          </x14:formula1>
-          <xm:sqref>C6</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789F72C4-22B4-0242-AA9D-05DCD1C7C1AF}">
-  <dimension ref="A1:O22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789F72C4-22B4-0242-AA9D-05DCD1C7C1AF}">
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="30" style="6" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="6" hidden="1" customWidth="1"/>
     <col min="5" max="6" width="20.1640625" style="6" customWidth="1"/>
     <col min="7" max="7" width="25.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="43.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="38" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="44.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="7.5" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>28</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="31"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
+      <c r="A4" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8" t="str" cm="1">
-        <f t="array" ref="D6">_xlfn.IFS(テーブル32[[#This Row],[Soft / Hard Delete]]="Soft Delete","SOFT_DELETE",テーブル32[[#This Row],[Soft / Hard Delete]]="Hard Delete","HARD_DELETE",TRUE,"")</f>
+      <c r="A5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.IFS(テーブル32[[#This Row],[Soft / Hard Delete]]="Soft Delete","SOFT_DELETE",テーブル32[[#This Row],[Soft / Hard Delete]]="Hard Delete","HARD_DELETE",TRUE,"")</f>
         <v/>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="N6" s="8"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="N5" s="8"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>50</v>
-      </c>
+      <c r="A12" s="15"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
-        <v>61</v>
-      </c>
+      <c r="A13" s="15"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="E4:G4"/>
+  <mergeCells count="2">
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:O3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{E3BC52CA-F4F7-924F-B0AE-BE775CF85BC2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{8F6F98C1-595C-9F49-B250-21CD2634841D}">
       <formula1>"Soft Delete,Hard Delete"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I6" xr:uid="{8EBE8BBE-C17C-4044-92F3-9326605ED5BB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5 N5" xr:uid="{7B8B2790-6C59-604D-89F1-3BD24DE216A5}">
+      <formula1>"quotes('),(none)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5" xr:uid="{77C8DCE9-D337-B146-99D9-21A4944967AD}">
       <formula1>"LocalDateTime,OffsetDateTime"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6 N6" xr:uid="{7D3FFFB4-A8E2-D545-A90A-66BF8D537200}">
-      <formula1>"quotes('),(none)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -2439,7 +2456,7 @@
           <x14:formula1>
             <xm:f>dropdown!$B$2:$B$20</xm:f>
           </x14:formula1>
-          <xm:sqref>N7</xm:sqref>
+          <xm:sqref>N6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2449,66 +2466,55 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E1BEA4-8682-2D4B-83F3-E3D5D9773981}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.83203125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="6" customWidth="1"/>
     <col min="5" max="16384" width="7.5" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
+      <c r="A4" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>65</v>
-      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C7" xr:uid="{F3EDCD97-3DDD-0A4D-ACDF-687A95CDC907}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C6" xr:uid="{F3EDCD97-3DDD-0A4D-ACDF-687A95CDC907}">
       <formula1>"quotes('),(none)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2522,27 +2528,27 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A480BCC2-429D-064C-9186-E29D7E93B50F}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.5" style="6" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="39.1640625" style="6" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="43.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="36.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="41.5" style="6" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="30.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5" style="6" customWidth="1"/>
+    <col min="9" max="9" width="32" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.5" style="6" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="7.5" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2550,87 +2556,85 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="31"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="27" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
+      <c r="F4" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="25" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>46</v>
-      </c>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="str" cm="1">
+        <f t="array" ref="C5">_xlfn.IFS(テーブル3236[[#This Row],[Related Table Process Pattern]]="Delete","DELETE",テーブル3236[[#This Row],[Related Table Process Pattern]]="Check and Skip Delete","CHECK_AND_SKIP_DELETE",TRUE,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="str" cm="1">
-        <f t="array" ref="C6">_xlfn.IFS(テーブル3236[[#This Row],[Related Table Process Pattern]]="Delete","DELETE",テーブル3236[[#This Row],[Related Table Process Pattern]]="Check and Skip Delete","CHECK_AND_SKIP_DELETE",TRUE,"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
+      <c r="B6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="8"/>
       <c r="B7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="20"/>
+      <c r="F7" s="18"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
@@ -2639,45 +2643,24 @@
       <c r="L7" s="15"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="A8" s="15"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
-        <v>61</v>
-      </c>
+      <c r="A9" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H4:L4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="A4:B4"/>
+  <mergeCells count="1">
+    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:G8" xr:uid="{F353BD13-7B61-C54A-8C2B-F025D3AA26B4}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G7" xr:uid="{F353BD13-7B61-C54A-8C2B-F025D3AA26B4}">
       <formula1>"quotes('),(none)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B8" xr:uid="{9B87489A-16BF-C040-BD48-9AF02F137779}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B7" xr:uid="{9B87489A-16BF-C040-BD48-9AF02F137779}">
+      <formula1>"Related Table Soft/Hard Delete,Data Check for Target Table Soft/Hard Delete"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{30AEF688-100C-C24A-A54E-53A83922E012}">
       <formula1>"Delete,Check and Skip Delete"</formula1>
     </dataValidation>
   </dataValidations>
